--- a/deployment_assets/offerlens_batch2_offers.xlsx
+++ b/deployment_assets/offerlens_batch2_offers.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O30"/>
+  <dimension ref="A1:O34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2448,6 +2448,276 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Bata</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Axis Bank</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Credit Card</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="n">
+        <v>2999</v>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Rs 500 off at Bata with Axis Bank Credit and Debit Cards.</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>Minimum shopping of Rs 2,999. Valid on Credit and Debit Cards.</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bata.in</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.axis.bank.in/offers</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>AJIO</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Axis Bank</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Credit Card</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="n">
+        <v>1299</v>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Flat Rs 150 off on AJIO with Axis Bank Credit and Debit Cards.</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>Minimum order value Rs 1,299. Valid on Credit and Debit Cards.</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>ADNAJIO</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ajio.com</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.axis.bank.in/offers</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Urban Ladder</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Axis Bank</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Shopping</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Credit Card</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Percentage</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Additional 10% off on Urban Ladder with Axis Bank Credit and Debit Cards.</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>Minimum order Rs 5,000. Stated as an additional discount, so it applies on top of any existing offer. No cap published by the issuer.</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>ULADN10</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.urbanladder.com</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.axis.bank.in/offers</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Yes Madam</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Axis Bank</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Health &amp; Beauty</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Credit Card</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Rs 500 off on Yes Madam with Axis Bank Credit and Debit Cards.</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>Minimum order not published by the issuer.</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>YMADN500</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yesmadam.com</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.axis.bank.in/offers</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2459,7 +2729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A32"/>
+  <dimension ref="A1:A34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -2478,7 +2748,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Built 30 July 2026. 29 offers across 9 issuers.</t>
+          <t>Built 30 July 2026. 33 offers across 10 issuers.</t>
         </is>
       </c>
     </row>
@@ -2662,6 +2932,20 @@
       <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Citibank - has exited Indian consumer banking; no such card exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Axis KFC (free fries) - a freebie, not a discount value; does not fit the schema.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Axis SNITCH and the Apple banner - headline only, no value published.</t>
         </is>
       </c>
     </row>
